--- a/plantillas/1_importadores.xlsx
+++ b/plantillas/1_importadores.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\USUARIO\Documentos\GitHub\sistema-importaciones1\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE114E04-A7A8-4575-99C6-EECC72C0FF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C740F831-3B56-4345-8007-83B9AD0C49EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11295" xr2:uid="{2E18EC6E-66FD-4066-B1B6-075CD0A07514}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2E18EC6E-66FD-4066-B1B6-075CD0A07514}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,12 +39,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>razon_social</t>
   </si>
   <si>
     <t>ruc</t>
+  </si>
+  <si>
+    <t>20609712849</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDOR FEY S.A.C</t>
+  </si>
+  <si>
+    <t>20612143651</t>
+  </si>
+  <si>
+    <t>T-IMPORTA PERU SAC</t>
   </si>
 </sst>
 </file>
@@ -68,7 +80,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -76,12 +88,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,18 +441,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EDC9099-A4FE-4389-808F-FD70C239A1DA}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{C26CCB4B-6828-463D-934F-17182FE5195B}">
+      <formula1>11</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>